--- a/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.06%2375</t>
+          <t>+1.47%2410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.06%</t>
+          <t>+1.47%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2375</v>
+        <v>2410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.18%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.79%5985</t>
+          <t>-5.1%5680</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5985</v>
+        <v>5680</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.88%1140</t>
+          <t>-4.82%1085</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.88%</t>
+          <t>-4.82%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1140</v>
+        <v>1085</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-3.55%2985</t>
+          <t>-4.02%2865</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-3.55%</t>
+          <t>-4.02%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>2985</v>
+        <v>2865</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.19%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-3.77%3700</t>
+          <t>+2.43%3790</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-3.77%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3700</v>
+        <v>3790</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0%115.5</t>
+          <t>+0.87%116.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.87%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>115.5</v>
+        <v>116.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+7.52%5650</t>
+          <t>-3.27%5465</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+7.52%</t>
+          <t>-3.27%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5650</v>
+        <v>5465</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+2.56%5600</t>
+          <t>-3.66%5395</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-3.66%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5600</v>
+        <v>5395</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.43%562</t>
+          <t>-1.42%554</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.43%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.13%1745</t>
+          <t>+0.29%1750</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>+0.29%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1745</v>
+        <v>1750</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.94%2105</t>
+          <t>-3.33%2035</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.94%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>2105</v>
+        <v>2035</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+0.34%590</t>
+          <t>-0.51%587</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-0.78%6325</t>
+          <t>-1.11%6255</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.78%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6325</v>
+        <v>6255</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.24%851</t>
+          <t>-4.7%811</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>851</v>
+        <v>811</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:01</t>
+          <t>2026-08-21 14:42:29</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-0.63%5515</t>
+          <t>+1.72%5610</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5515</v>
+        <v>5610</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.27%1195</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1195</v>
+        <v>1135</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+6.33%5630</t>
+          <t>-0.53%5600</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+6.33%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5630</v>
+        <v>5600</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.51%15750</t>
+          <t>-2.54%15350</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>-2.54%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>15750</v>
+        <v>15350</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.02%993</t>
+          <t>-5.24%941</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.02%</t>
+          <t>-5.24%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>993</v>
+        <v>941</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+2.27%2250</t>
+          <t>+1.11%2275</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+2.27%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2250</v>
+        <v>2275</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+5%1575</t>
+          <t>-5.08%1495</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+5%</t>
+          <t>-5.08%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1575</v>
+        <v>1495</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+5.06%176.5</t>
+          <t>+2.55%181</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+5.06%</t>
+          <t>+2.55%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>176.5</v>
+        <v>181</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.94%2140</t>
+          <t>-1.87%2100</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.94%</t>
+          <t>-1.87%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2140</v>
+        <v>2100</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0%1135</t>
+          <t>-3.96%1090</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.96%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1135</v>
+        <v>1090</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-0.8%186</t>
+          <t>+3.23%192</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>+3.23%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+2.29%268.5</t>
+          <t>-0.37%267.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+2.29%</t>
+          <t>-0.37%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>268.5</v>
+        <v>267.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0%1850</t>
+          <t>-4.59%1765</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-4.59%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1850</v>
+        <v>1765</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.47%553</t>
+          <t>-0.36%551</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-0.62%1610</t>
+          <t>-0.93%1595</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1610</v>
+        <v>1595</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:02</t>
+          <t>2026-08-21 14:42:31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.16%6455</t>
+          <t>-0.77%6405</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.77%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>6455</v>
+        <v>6405</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.61%246.5</t>
+          <t>-0.41%245.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>246.5</v>
+        <v>245.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.79%355</t>
+          <t>-1.27%350.5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-1.27%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>355</v>
+        <v>350.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.99%713</t>
+          <t>-1.26%704</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+2.52%122</t>
+          <t>+0.41%122.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+2.52%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>122</v>
+        <v>122.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+1.63%1555</t>
+          <t>-1.93%1525</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+1.63%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1555</v>
+        <v>1525</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.73%413.5</t>
+          <t>+5.44%436</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>413.5</v>
+        <v>436</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.58%567</t>
+          <t>-0.18%566</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.27%698</t>
+          <t>-2.72%679</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.27%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.21%13925</t>
+          <t>-3.88%13385</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>-3.88%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>13925</v>
+        <v>13385</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.83%1075</t>
+          <t>-1.4%1060</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.83%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1075</v>
+        <v>1060</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+1.31%463</t>
+          <t>-4.75%441</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>-4.75%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.86%70.2</t>
+          <t>+1.99%71.6</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.86%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>70.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.97%208.5</t>
+          <t>-2.64%203</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>-2.64%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>208.5</v>
+        <v>203</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+1.47%138.5</t>
+          <t>-3.97%133</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.47%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>138.5</v>
+        <v>133</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:03</t>
+          <t>2026-08-21 14:42:32</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+0.64%237</t>
+          <t>-0.63%235.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>237</v>
+        <v>235.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:05</t>
+          <t>2026-08-21 14:42:33</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+3.91%412</t>
+          <t>-1.46%406</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+3.91%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:05</t>
+          <t>2026-08-21 14:42:33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.53%1995</t>
+          <t>+4.01%2075</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.53%</t>
+          <t>+4.01%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1995</v>
+        <v>2075</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:05</t>
+          <t>2026-08-21 14:42:33</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-0.8%496</t>
+          <t>-1.11%490.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>496</v>
+        <v>490.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:05</t>
+          <t>2026-08-21 14:42:33</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.14%366.5</t>
+          <t>-4.77%349</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-4.77%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>366.5</v>
+        <v>349</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 08:47:05</t>
+          <t>2026-08-21 14:42:33</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.32%153.5</t>
+          <t>-1.3%151.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>153.5</v>
+        <v>151.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:29</t>
+          <t>2026-08-21 14:54:55</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:31</t>
+          <t>2026-08-21 14:54:56</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:32</t>
+          <t>2026-08-21 14:54:58</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:33</t>
+          <t>2026-08-21 14:54:59</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:33</t>
+          <t>2026-08-21 14:54:59</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:33</t>
+          <t>2026-08-21 14:54:59</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:33</t>
+          <t>2026-08-21 14:54:59</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:42:33</t>
+          <t>2026-08-21 14:54:59</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:55</t>
+          <t>2026-08-21 16:07:27</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:56</t>
+          <t>2026-08-21 16:07:28</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:58</t>
+          <t>2026-08-21 16:07:29</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 14:54:59</t>
+          <t>2026-08-21 16:07:31</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:27</t>
+          <t>2026-08-21 16:41:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:28</t>
+          <t>2026-08-21 16:41:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:29</t>
+          <t>2026-08-21 16:41:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:31</t>
+          <t>2026-08-21 16:41:08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:31</t>
+          <t>2026-08-21 16:41:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:31</t>
+          <t>2026-08-21 16:41:08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:31</t>
+          <t>2026-08-21 16:41:08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:07:31</t>
+          <t>2026-08-21 16:41:08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16.66%12,000,000</t>
+          <t>17.12%12,000,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.66%</t>
+          <t>17.12%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.91%1,690,000</t>
+          <t>5.68%1,690,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.91%</t>
+          <t>5.68%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>-0.30%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.64%8,460,000</t>
+          <t>5.43%8,460,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.64%</t>
+          <t>5.43%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.28%</t>
+          <t>-0.27%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.23%3,000,000</t>
+          <t>5.09%3,000,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.23%</t>
+          <t>5.09%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.56%2,110,000</t>
+          <t>4.73%2,110,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.56%</t>
+          <t>4.73%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.05%60,000,000</t>
+          <t>4.14%60,000,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>4.14%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.63%1,100,000</t>
+          <t>3.56%1,100,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.63%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.54%1,080,000</t>
+          <t>3.45%1,080,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.45%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.10%3,040,000</t>
+          <t>3.15%3,040,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.84%2,307,000</t>
+          <t>2.78%2,307,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.84%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.76%8,000,000</t>
+          <t>2.78%8,000,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.7%811</t>
+          <t>+1.72%5610</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>+1.72%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>811</v>
+        <v>5610</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.11%4,250,000</t>
+          <t>2.08%626,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4250000</v>
+        <v>626000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:04</t>
+          <t>2026-08-21 17:28:10</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+1.72%5610</t>
+          <t>-4.7%811</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-4.7%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5610</v>
+        <v>811</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.02%626,000</t>
+          <t>2.04%4,250,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>626000</v>
+        <v>4250000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-5.02%1135</t>
+          <t>-0.53%5600</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-5.02%</t>
+          <t>-0.53%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1135</v>
+        <v>5600</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.84%2,640,000</t>
+          <t>2.02%610,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.84%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2640000</v>
+        <v>610000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-0.53%5600</t>
+          <t>-5.02%1135</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-0.53%</t>
+          <t>-5.02%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5600</v>
+        <v>1135</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.81%550,000</t>
+          <t>1.77%2,640,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>550000</v>
+        <v>2640000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.65%179,500</t>
+          <t>1.63%179,500</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-5.24%941</t>
+          <t>+1.11%2275</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-5.24%</t>
+          <t>+1.11%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>941</v>
+        <v>2275</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.63%2,800,000</t>
+          <t>1.62%1,200,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.63%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>2800000</v>
+        <v>1200000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.11%2275</t>
+          <t>+2.55%181</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>+2.55%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2275</v>
+        <v>181</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.58%1,200,000</t>
+          <t>1.61%15,000,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1200000</v>
+        <v>15000000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,16 +1742,16 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.55%1,680,000</t>
+          <t>1.59%1,800,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>1680000</v>
+        <v>1800000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+2.55%181</t>
+          <t>-5.24%941</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+2.55%</t>
+          <t>-5.24%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>181</v>
+        <v>941</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.55%15,000,000</t>
+          <t>1.56%2,800,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>15000000</v>
+        <v>2800000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.25%1,000,000</t>
+          <t>1.24%1,000,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.06%1,600,000</t>
+          <t>1.03%1,600,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.03%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,12 +1986,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.98%9,000,000</t>
+          <t>1.02%9,000,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.84%5,360,000</t>
+          <t>0.85%5,360,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.76%700,000</t>
+          <t>0.73%700,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.73%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.58%1,800,000</t>
+          <t>0.59%1,800,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.49%525,000</t>
+          <t>0.50%525,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:05</t>
+          <t>2026-08-21 17:28:11</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.42%2,000,000</t>
+          <t>0.41%2,000,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.26%704</t>
+          <t>+0.41%122.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.26%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>704</v>
+        <v>122.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.33%800,000</t>
+          <t>0.33%4,500,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,11 +2483,11 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>800000</v>
+        <v>4500000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+0.41%122.5</t>
+          <t>-1.26%704</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-1.26%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>122.5</v>
+        <v>704</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.32%4,500,000</t>
+          <t>0.33%800,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>4500000</v>
+        <v>800000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-1.93%1525</t>
+          <t>+5.44%436</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-1.93%</t>
+          <t>+5.44%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1525</v>
+        <v>436</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.20%225,000</t>
+          <t>0.21%800,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>225000</v>
+        <v>800000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2639,38 +2639,38 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+5.44%436</t>
+          <t>-1.93%1525</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+5.44%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>436</v>
+        <v>1525</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.19%800,000</t>
+          <t>0.20%225,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>800000</v>
+        <v>225000</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.14%500,000</t>
+          <t>0.13%500,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.10%2,500,000</t>
+          <t>0.11%2,500,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.09%700,000</t>
+          <t>0.08%700,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,34 +3127,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-3.97%133</t>
+          <t>-0.63%235.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.97%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>133</v>
+        <v>235.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.06%700,000</t>
+          <t>0.05%350,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>700000</v>
+        <v>350000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:07</t>
+          <t>2026-08-21 17:28:12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>2455全新</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.63%235.5</t>
+          <t>-1.46%406</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.63%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>235.5</v>
+        <v>406</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.05%350,000</t>
+          <t>0.05%200,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>350000</v>
+        <v>200000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:08</t>
+          <t>2026-08-21 17:28:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2455全新</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.46%406</t>
+          <t>+4.01%2075</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+4.01%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>406</v>
+        <v>2075</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.05%200,000</t>
+          <t>0%1,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>200000</v>
+        <v>1000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:08</t>
+          <t>2026-08-21 17:28:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,21 +3310,21 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+4.01%2075</t>
+          <t>-1.11%490.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+4.01%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2075</v>
+        <v>490.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:08</t>
+          <t>2026-08-21 17:28:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>2049上銀</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.11%490.5</t>
+          <t>-4.77%349</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.11%</t>
+          <t>-4.77%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>490.5</v>
+        <v>349</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:08</t>
+          <t>2026-08-21 17:28:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2049上銀</t>
+          <t>5347世界</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-4.77%349</t>
+          <t>-1.3%151.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-4.77%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>349</v>
+        <v>151.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 16:41:08</t>
+          <t>2026-08-21 17:28:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>2481強茂</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.3%151.5</t>
+          <t>-3.97%133</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>151.5</v>
+        <v>133</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-21_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:10</t>
+          <t>2026-08-21 20:06:19</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:11</t>
+          <t>2026-08-21 20:06:21</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:12</t>
+          <t>2026-08-21 20:06:22</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:13</t>
+          <t>2026-08-21 20:06:23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:13</t>
+          <t>2026-08-21 20:06:23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:13</t>
+          <t>2026-08-21 20:06:23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:13</t>
+          <t>2026-08-21 20:06:23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-21 17:28:13</t>
+          <t>2026-08-21 20:06:23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
